--- a/Historial_cotizaciones.xlsx
+++ b/Historial_cotizaciones.xlsx
@@ -1,50 +1,113 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\cotizador-web-mp\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D171B221-34E3-495B-AAD5-D9BFBFA56756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Historial" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
+  <si>
+    <t>N° Cotización</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Proyecto</t>
+  </si>
+  <si>
+    <t>Comuna</t>
+  </si>
+  <si>
+    <t>N° Unidad</t>
+  </si>
+  <si>
+    <t>Tipo Unidad</t>
+  </si>
+  <si>
+    <t>Broker/Cliente</t>
+  </si>
+  <si>
+    <t>Valor Venta UF</t>
+  </si>
+  <si>
+    <t>Crédito Hip. UF</t>
+  </si>
+  <si>
+    <t>Pie %</t>
+  </si>
+  <si>
+    <t>COT-2026-0005</t>
+  </si>
+  <si>
+    <t>31 de marzo de 2026</t>
+  </si>
+  <si>
+    <t>ALTO BUZETA (MT)</t>
+  </si>
+  <si>
+    <t>Cerrillos</t>
+  </si>
+  <si>
+    <t>Departamento</t>
+  </si>
+  <si>
+    <t>Verónica Valdés</t>
+  </si>
+  <si>
+    <t>COT-2026-0004</t>
+  </si>
+  <si>
+    <t>Felipe Donoso</t>
+  </si>
+  <si>
+    <t>COT-2026-0003</t>
+  </si>
+  <si>
+    <t>JARDINES DE ALVARADO</t>
+  </si>
+  <si>
+    <t>Independencia</t>
+  </si>
+  <si>
+    <t>jp</t>
+  </si>
+  <si>
+    <t>COT-2026-0002</t>
+  </si>
+  <si>
+    <t>felipe donoso</t>
+  </si>
+  <si>
+    <t>COT-2026-0001</t>
+  </si>
+  <si>
+    <t>juan perez</t>
+  </si>
+  <si>
+    <t>Corredor</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="10">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0;[Red]&quot;$&quot;\-#,##0"/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="[$$]#,##0"/>
-    <numFmt numFmtId="166" formatCode="[$UF]#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="[$UF]#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="0.000000%"/>
-    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -74,13 +137,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6392AFE7-D39C-4622-AC8C-E6765621BD07}"/>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -405,74 +478,77 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="25.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.796875" customWidth="1"/>
+    <col min="2" max="2" width="14.796875" customWidth="1"/>
+    <col min="3" max="3" width="30.796875" customWidth="1"/>
+    <col min="4" max="4" width="16.796875" customWidth="1"/>
+    <col min="5" max="5" width="10.796875" customWidth="1"/>
+    <col min="6" max="6" width="14.796875" customWidth="1"/>
+    <col min="7" max="7" width="25.796875" customWidth="1"/>
+    <col min="8" max="9" width="15.796875" customWidth="1"/>
+    <col min="10" max="10" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>N° Cotización</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Fecha</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Proyecto</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Comuna</v>
-      </c>
-      <c r="E1" t="str">
-        <v>N° Unidad</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Tipo Unidad</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Broker/Cliente</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Valor Venta UF</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Crédito Hip. UF</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Pie %</v>
+    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>COT-2026-0005</v>
-      </c>
-      <c r="B2" t="str">
-        <v>31 de marzo de 2026</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ALTO BUZETA (MT)</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Cerrillos</v>
+    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
       </c>
       <c r="E2">
         <v>1813</v>
       </c>
-      <c r="F2" t="str">
-        <v>Departamento</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Verónica Valdés</v>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
       </c>
       <c r="H2">
         <v>3328.3</v>
@@ -484,27 +560,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>COT-2026-0004</v>
-      </c>
-      <c r="B3" t="str">
-        <v>31 de marzo de 2026</v>
-      </c>
-      <c r="C3" t="str">
-        <v>ALTO BUZETA (MT)</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Cerrillos</v>
+    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
       </c>
       <c r="E3">
         <v>813</v>
       </c>
-      <c r="F3" t="str">
-        <v>Departamento</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Felipe Donoso</v>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
       </c>
       <c r="H3">
         <v>2802.6</v>
@@ -516,27 +592,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>COT-2026-0003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>31 de marzo de 2026</v>
-      </c>
-      <c r="C4" t="str">
-        <v>JARDINES DE ALVARADO</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Independencia</v>
+    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
       </c>
       <c r="E4">
         <v>217</v>
       </c>
-      <c r="F4" t="str">
-        <v>Departamento</v>
-      </c>
-      <c r="G4" t="str">
-        <v>jp</v>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
       </c>
       <c r="H4">
         <v>2349.87</v>
@@ -548,27 +624,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>COT-2026-0002</v>
-      </c>
-      <c r="B5" t="str">
-        <v>31 de marzo de 2026</v>
-      </c>
-      <c r="C5" t="str">
-        <v>ALTO BUZETA (MT)</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Cerrillos</v>
+    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
       </c>
       <c r="E5">
         <v>809</v>
       </c>
-      <c r="F5" t="str">
-        <v>Departamento</v>
-      </c>
-      <c r="G5" t="str">
-        <v>felipe donoso</v>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
       </c>
       <c r="H5">
         <v>2781</v>
@@ -580,27 +656,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>COT-2026-0001</v>
-      </c>
-      <c r="B6" t="str">
-        <v>31 de marzo de 2026</v>
-      </c>
-      <c r="C6" t="str">
-        <v>ALTO BUZETA (MT)</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Cerrillos</v>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
       </c>
       <c r="E6">
         <v>808</v>
       </c>
-      <c r="F6" t="str">
-        <v>Departamento</v>
-      </c>
-      <c r="G6" t="str">
-        <v>juan perez</v>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
       </c>
       <c r="H6">
         <v>2781</v>
@@ -613,8 +689,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError sqref="A1:J6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Historial_cotizaciones.xlsx
+++ b/Historial_cotizaciones.xlsx
@@ -1,26 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\cotizador-web-mp\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D171B221-34E3-495B-AAD5-D9BFBFA56756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Historial" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Historial" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>N° Cotización</t>
   </si>
@@ -52,68 +43,41 @@
     <t>Pie %</t>
   </si>
   <si>
-    <t>COT-2026-0005</t>
-  </si>
-  <si>
-    <t>31 de marzo de 2026</t>
-  </si>
-  <si>
-    <t>ALTO BUZETA (MT)</t>
-  </si>
-  <si>
-    <t>Cerrillos</t>
+    <t>Corredor</t>
+  </si>
+  <si>
+    <t>TEST-0001</t>
+  </si>
+  <si>
+    <t>10-04-2026</t>
+  </si>
+  <si>
+    <t>PROYECTO TEST</t>
+  </si>
+  <si>
+    <t>Santiago</t>
   </si>
   <si>
     <t>Departamento</t>
   </si>
   <si>
-    <t>Verónica Valdés</t>
-  </si>
-  <si>
-    <t>COT-2026-0004</t>
-  </si>
-  <si>
-    <t>Felipe Donoso</t>
-  </si>
-  <si>
-    <t>COT-2026-0003</t>
-  </si>
-  <si>
-    <t>JARDINES DE ALVARADO</t>
-  </si>
-  <si>
-    <t>Independencia</t>
-  </si>
-  <si>
-    <t>jp</t>
-  </si>
-  <si>
-    <t>COT-2026-0002</t>
-  </si>
-  <si>
-    <t>felipe donoso</t>
-  </si>
-  <si>
-    <t>COT-2026-0001</t>
-  </si>
-  <si>
-    <t>juan perez</t>
-  </si>
-  <si>
-    <t>Corredor</t>
+    <t>Juan Test</t>
+  </si>
+  <si>
+    <t>Corredor Test</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -143,9 +107,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6392AFE7-D39C-4622-AC8C-E6765621BD07}"/>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -478,22 +440,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.796875" customWidth="1"/>
-    <col min="2" max="2" width="14.796875" customWidth="1"/>
-    <col min="3" max="3" width="30.796875" customWidth="1"/>
-    <col min="4" max="4" width="16.796875" customWidth="1"/>
-    <col min="5" max="5" width="10.796875" customWidth="1"/>
-    <col min="6" max="6" width="14.796875" customWidth="1"/>
-    <col min="7" max="7" width="25.796875" customWidth="1"/>
-    <col min="8" max="9" width="15.796875" customWidth="1"/>
-    <col min="10" max="10" width="8.796875" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -525,173 +476,46 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>1813</v>
+        <v>101</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2">
-        <v>3328.3</v>
+        <v>2800</v>
       </c>
       <c r="I2">
-        <v>3161.89</v>
+        <v>2500</v>
       </c>
       <c r="J2">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>813</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="K2" t="s">
         <v>17</v>
-      </c>
-      <c r="H3">
-        <v>2802.6</v>
-      </c>
-      <c r="I3">
-        <v>2522.34</v>
-      </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4">
-        <v>217</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4">
-        <v>2349.87</v>
-      </c>
-      <c r="I4">
-        <v>2114.88</v>
-      </c>
-      <c r="J4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5">
-        <v>809</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5">
-        <v>2781</v>
-      </c>
-      <c r="I5">
-        <v>2641.95</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6">
-        <v>808</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6">
-        <v>2781</v>
-      </c>
-      <c r="I6">
-        <v>2502.9</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:J6" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/Historial_cotizaciones.xlsx
+++ b/Historial_cotizaciones.xlsx
@@ -1,83 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet sheetId="1" name="Historial" state="visible" r:id="rId4"/>
+    <sheet name="Historial" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t>N° Cotización</t>
-  </si>
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Proyecto</t>
-  </si>
-  <si>
-    <t>Comuna</t>
-  </si>
-  <si>
-    <t>N° Unidad</t>
-  </si>
-  <si>
-    <t>Tipo Unidad</t>
-  </si>
-  <si>
-    <t>Broker/Cliente</t>
-  </si>
-  <si>
-    <t>Valor Venta UF</t>
-  </si>
-  <si>
-    <t>Crédito Hip. UF</t>
-  </si>
-  <si>
-    <t>Pie %</t>
-  </si>
-  <si>
-    <t>Corredor</t>
-  </si>
-  <si>
-    <t>TEST-0001</t>
-  </si>
-  <si>
-    <t>10-04-2026</t>
-  </si>
-  <si>
-    <t>PROYECTO TEST</t>
-  </si>
-  <si>
-    <t>Santiago</t>
-  </si>
-  <si>
-    <t>Departamento</t>
-  </si>
-  <si>
-    <t>Juan Test</t>
-  </si>
-  <si>
-    <t>Corredor Test</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -101,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -440,82 +396,1460 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K41"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="10" max="10" width="7.83203125" customWidth="1"/>
+    <col min="11" max="11" width="25.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>N° Cotización</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Fecha</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Proyecto</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Comuna</v>
+      </c>
+      <c r="E1" t="str">
+        <v>N° Unidad</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Tipo Unidad</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Broker/Cliente</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Valor Venta UF</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Crédito Hip. UF</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Pie %</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Corredor</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>COT-2026-0040</v>
+      </c>
+      <c r="B2" t="str">
+        <v>10-04-2026</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E2">
+        <v>1601</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G2" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H2">
+        <v>2887.53</v>
+      </c>
+      <c r="I2">
+        <v>2598.78</v>
+      </c>
+      <c r="J2">
+        <v>10</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>COT-2026-0039</v>
+      </c>
+      <c r="B3" t="str">
+        <v>09-04-2026</v>
+      </c>
+      <c r="C3" t="str">
+        <v>PLAZA QUILICURA</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Quilicura</v>
+      </c>
+      <c r="E3">
+        <v>207</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G3" t="str">
+        <v>gian</v>
+      </c>
+      <c r="H3">
+        <v>2214</v>
+      </c>
+      <c r="I3">
+        <v>1992.6</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>COT-2026-0038</v>
+      </c>
+      <c r="B4" t="str">
+        <v>07-04-2026</v>
+      </c>
+      <c r="C4" t="str">
+        <v>VALLE LOS INGLESES</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Valparaiso</v>
+      </c>
+      <c r="E4">
+        <v>1804</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G4" t="str">
+        <v>María José Martínez Morales</v>
+      </c>
+      <c r="H4">
+        <v>4848</v>
+      </c>
+      <c r="I4">
+        <v>3878.4</v>
+      </c>
+      <c r="J4">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>101</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2">
-        <v>2800</v>
-      </c>
-      <c r="I2">
-        <v>2500</v>
-      </c>
-      <c r="J2">
-        <v>10</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>COT-2026-0037</v>
+      </c>
+      <c r="B5" t="str">
+        <v>07-04-2026</v>
+      </c>
+      <c r="C5" t="str">
+        <v>VALLE LOS INGLESES</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Valparaiso</v>
+      </c>
+      <c r="E5">
+        <v>1804</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G5" t="str">
+        <v>mjm</v>
+      </c>
+      <c r="H5">
+        <v>4848</v>
+      </c>
+      <c r="I5">
+        <v>3878.4</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>COT-2026-0036</v>
+      </c>
+      <c r="B6" t="str">
+        <v>07-04-2026</v>
+      </c>
+      <c r="C6" t="str">
+        <v>JARDINES DE ALVARADO</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Independencia</v>
+      </c>
+      <c r="E6">
+        <v>714</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G6" t="str">
+        <v>fd</v>
+      </c>
+      <c r="H6">
+        <v>2932.56</v>
+      </c>
+      <c r="I6">
+        <v>2639.3</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>COT-2026-0035</v>
+      </c>
+      <c r="B7" t="str">
+        <v>06-04-2026</v>
+      </c>
+      <c r="C7" t="str">
+        <v>JARDINES DE ALVARADO</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Independencia</v>
+      </c>
+      <c r="E7">
+        <v>812</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G7" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H7">
+        <v>2191.53</v>
+      </c>
+      <c r="I7">
+        <v>1972.38</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>COT-2026-0034</v>
+      </c>
+      <c r="B8" t="str">
+        <v>05-04-2026</v>
+      </c>
+      <c r="C8" t="str">
+        <v>VALLE LOS INGLESES</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Valparaiso</v>
+      </c>
+      <c r="E8">
+        <v>1804</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G8" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H8">
+        <v>4848</v>
+      </c>
+      <c r="I8">
+        <v>3878.4</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>COT-2026-0033</v>
+      </c>
+      <c r="B9" t="str">
+        <v>05-04-2026</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E9">
+        <v>1601</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G9" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H9">
+        <v>3317.53</v>
+      </c>
+      <c r="I9">
+        <v>2985.78</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>COT-2026-0032</v>
+      </c>
+      <c r="B10" t="str">
+        <v>05-04-2026</v>
+      </c>
+      <c r="C10" t="str">
+        <v>VALLE LOS INGLESES</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Valparaiso</v>
+      </c>
+      <c r="E10">
+        <v>1804</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G10" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H10">
+        <v>4848</v>
+      </c>
+      <c r="I10">
+        <v>3878.4</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>COT-2026-0031</v>
+      </c>
+      <c r="B11" t="str">
+        <v>05-04-2026</v>
+      </c>
+      <c r="C11" t="str">
+        <v>VALLE LOS INGLESES</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Valparaiso</v>
+      </c>
+      <c r="E11">
+        <v>1804</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G11" t="str">
+        <v>VV</v>
+      </c>
+      <c r="H11">
+        <v>4848</v>
+      </c>
+      <c r="I11">
+        <v>3878.4</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>COT-2026-0030</v>
+      </c>
+      <c r="B12" t="str">
+        <v>05-04-2026</v>
+      </c>
+      <c r="C12" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E12">
+        <v>1601</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G12" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H12">
+        <v>3317.53</v>
+      </c>
+      <c r="I12">
+        <v>2985.78</v>
+      </c>
+      <c r="J12">
+        <v>10</v>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>COT-2026-0029</v>
+      </c>
+      <c r="B13" t="str">
+        <v>02-04-2026</v>
+      </c>
+      <c r="C13" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E13">
+        <v>1601</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G13" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H13">
+        <v>3317.53</v>
+      </c>
+      <c r="I13">
+        <v>2985.78</v>
+      </c>
+      <c r="J13">
+        <v>10</v>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>COT-2026-0028</v>
+      </c>
+      <c r="B14" t="str">
+        <v>02-04-2026</v>
+      </c>
+      <c r="C14" t="str">
+        <v>VALLE LOS INGLESES</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Valparaiso</v>
+      </c>
+      <c r="E14">
+        <v>1804</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G14" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H14">
+        <v>4848</v>
+      </c>
+      <c r="I14">
+        <v>3878.4</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>COT-2026-0027</v>
+      </c>
+      <c r="B15" t="str">
+        <v>02-04-2026</v>
+      </c>
+      <c r="C15" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E15">
+        <v>1601</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G15" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H15">
+        <v>3317.53</v>
+      </c>
+      <c r="I15">
+        <v>2985.78</v>
+      </c>
+      <c r="J15">
+        <v>10</v>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>COT-2026-0026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>02-04-2026</v>
+      </c>
+      <c r="C16" t="str">
+        <v>VALLE LOS INGLESES</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Valparaiso</v>
+      </c>
+      <c r="E16">
+        <v>1804</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G16" t="str">
+        <v>VV</v>
+      </c>
+      <c r="H16">
+        <v>4848</v>
+      </c>
+      <c r="I16">
+        <v>5698.6</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>COT-2026-0025</v>
+      </c>
+      <c r="B17" t="str">
+        <v>02-04-2026</v>
+      </c>
+      <c r="C17" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E17">
+        <v>1601</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G17" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H17">
+        <v>3317.53</v>
+      </c>
+      <c r="I17">
+        <v>2985.78</v>
+      </c>
+      <c r="J17">
+        <v>10</v>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>COT-2026-0024</v>
+      </c>
+      <c r="B18" t="str">
+        <v>02-04-2026</v>
+      </c>
+      <c r="C18" t="str">
+        <v>VALLE LOS INGLESES</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Valparaiso</v>
+      </c>
+      <c r="E18">
+        <v>1804</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G18" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H18">
+        <v>4848</v>
+      </c>
+      <c r="I18">
+        <v>6060</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>COT-2026-0023</v>
+      </c>
+      <c r="B19" t="str">
+        <v>02-04-2026</v>
+      </c>
+      <c r="C19" t="str">
+        <v>VALLE LOS INGLESES</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Valparaiso</v>
+      </c>
+      <c r="E19">
+        <v>1804</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G19" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H19">
+        <v>4848</v>
+      </c>
+      <c r="I19">
+        <v>5748.34</v>
+      </c>
+      <c r="J19">
+        <v>10</v>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>COT-2026-0022</v>
+      </c>
+      <c r="B20" t="str">
+        <v>02-04-2026</v>
+      </c>
+      <c r="C20" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E20">
+        <v>1601</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G20" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H20">
+        <v>3317.53</v>
+      </c>
+      <c r="I20">
+        <v>2985.78</v>
+      </c>
+      <c r="J20">
+        <v>10</v>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>COT-2026-0021</v>
+      </c>
+      <c r="B21" t="str">
+        <v>02-04-2026</v>
+      </c>
+      <c r="C21" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E21">
+        <v>1601</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G21" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H21">
+        <v>3317.53</v>
+      </c>
+      <c r="I21">
+        <v>2985.78</v>
+      </c>
+      <c r="J21">
+        <v>10</v>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>COT-2026-0020</v>
+      </c>
+      <c r="B22" t="str">
+        <v>02-04-2026</v>
+      </c>
+      <c r="C22" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E22">
+        <v>1601</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G22" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H22">
+        <v>3317.53</v>
+      </c>
+      <c r="I22">
+        <v>3068.72</v>
+      </c>
+      <c r="J22">
+        <v>10</v>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>COT-2026-0019</v>
+      </c>
+      <c r="B23" t="str">
+        <v>02-04-2026</v>
+      </c>
+      <c r="C23" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E23">
+        <v>1601</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G23" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H23">
+        <v>3317.53</v>
+      </c>
+      <c r="I23">
+        <v>3068.72</v>
+      </c>
+      <c r="J23">
+        <v>10</v>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>COT-2026-0018</v>
+      </c>
+      <c r="B24" t="str">
+        <v>01-04-2026</v>
+      </c>
+      <c r="C24" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E24">
+        <v>1601</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G24" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H24">
+        <v>3317.53</v>
+      </c>
+      <c r="I24">
+        <v>3068.72</v>
+      </c>
+      <c r="J24">
+        <v>10</v>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>COT-2026-0017</v>
+      </c>
+      <c r="B25" t="str">
+        <v>01-04-2026</v>
+      </c>
+      <c r="C25" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E25">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G25" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H25">
+        <v>2866.65</v>
+      </c>
+      <c r="I25">
+        <v>2579.99</v>
+      </c>
+      <c r="J25">
+        <v>10</v>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>COT-2026-0016</v>
+      </c>
+      <c r="B26" t="str">
+        <v>01-04-2026</v>
+      </c>
+      <c r="C26" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E26">
+        <v>1601</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G26" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H26">
+        <v>3317.53</v>
+      </c>
+      <c r="I26">
+        <v>2985.78</v>
+      </c>
+      <c r="J26">
+        <v>10</v>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>COT-2026-0015</v>
+      </c>
+      <c r="B27" t="str">
+        <v>01-04-2026</v>
+      </c>
+      <c r="C27" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E27">
+        <v>813</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G27" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H27">
+        <v>2802.6</v>
+      </c>
+      <c r="I27">
+        <v>2522.34</v>
+      </c>
+      <c r="J27">
+        <v>10</v>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>COT-2026-0014</v>
+      </c>
+      <c r="B28" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="C28" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E28">
+        <v>1601</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Verónica Valdés</v>
+      </c>
+      <c r="H28">
+        <v>3317.53</v>
+      </c>
+      <c r="I28">
+        <v>2985.78</v>
+      </c>
+      <c r="J28">
+        <v>10</v>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>COT-2026-0013</v>
+      </c>
+      <c r="B29" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="C29" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E29">
+        <v>902</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G29" t="str">
+        <v>VV</v>
+      </c>
+      <c r="H29">
+        <v>3364.9</v>
+      </c>
+      <c r="I29">
+        <v>3028.41</v>
+      </c>
+      <c r="J29">
+        <v>10</v>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>COT-2026-0012</v>
+      </c>
+      <c r="B30" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="C30" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E30">
+        <v>913</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Verónica Valdés</v>
+      </c>
+      <c r="H30">
+        <v>3283.4</v>
+      </c>
+      <c r="I30">
+        <v>2955.06</v>
+      </c>
+      <c r="J30">
+        <v>10</v>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>COT-2026-0011</v>
+      </c>
+      <c r="B31" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="C31" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E31">
+        <v>1209</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Verónica Valdés</v>
+      </c>
+      <c r="H31">
+        <v>3283.4</v>
+      </c>
+      <c r="I31">
+        <v>2955.06</v>
+      </c>
+      <c r="J31">
+        <v>10</v>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>COT-2026-0010</v>
+      </c>
+      <c r="B32" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="C32" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E32">
+        <v>709</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Verónica Valdés</v>
+      </c>
+      <c r="H32">
+        <v>3230.2</v>
+      </c>
+      <c r="I32">
+        <v>2907.18</v>
+      </c>
+      <c r="J32">
+        <v>10</v>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>COT-2026-0009</v>
+      </c>
+      <c r="B33" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="C33" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E33">
+        <v>1101</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G33" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H33">
+        <v>3310.56</v>
+      </c>
+      <c r="I33">
+        <v>3145.02</v>
+      </c>
+      <c r="J33">
+        <v>10</v>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>COT-2026-0008</v>
+      </c>
+      <c r="B34" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="C34" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E34">
+        <v>1101</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G34" t="str">
+        <v>vv</v>
+      </c>
+      <c r="H34">
+        <v>2960.56</v>
+      </c>
+      <c r="I34">
+        <v>2664.5</v>
+      </c>
+      <c r="J34">
+        <v>10</v>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>COT-2026-0007</v>
+      </c>
+      <c r="B35" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="C35" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E35">
+        <v>602</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Verónica Valdés</v>
+      </c>
+      <c r="H35">
+        <v>3093.58</v>
+      </c>
+      <c r="I35">
+        <v>2784.22</v>
+      </c>
+      <c r="J35">
+        <v>10</v>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>COT-2026-0006</v>
+      </c>
+      <c r="B36" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="C36" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E36">
+        <v>609</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Felipe</v>
+      </c>
+      <c r="H36">
+        <v>3188.5</v>
+      </c>
+      <c r="I36">
+        <v>2869.65</v>
+      </c>
+      <c r="J36">
+        <v>10</v>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>COT-2026-0005</v>
+      </c>
+      <c r="B37" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="C37" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E37">
+        <v>1813</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Verónica Valdés</v>
+      </c>
+      <c r="H37">
+        <v>3328.3</v>
+      </c>
+      <c r="I37">
+        <v>3161.89</v>
+      </c>
+      <c r="J37">
+        <v>10</v>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>COT-2026-0004</v>
+      </c>
+      <c r="B38" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="C38" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E38">
+        <v>813</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Felipe Donoso</v>
+      </c>
+      <c r="H38">
+        <v>2802.6</v>
+      </c>
+      <c r="I38">
+        <v>2522.34</v>
+      </c>
+      <c r="J38">
+        <v>10</v>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>COT-2026-0003</v>
+      </c>
+      <c r="B39" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="C39" t="str">
+        <v>JARDINES DE ALVARADO</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Independencia</v>
+      </c>
+      <c r="E39">
+        <v>217</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G39" t="str">
+        <v>jp</v>
+      </c>
+      <c r="H39">
+        <v>2349.87</v>
+      </c>
+      <c r="I39">
+        <v>2114.88</v>
+      </c>
+      <c r="J39">
+        <v>10</v>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>COT-2026-0002</v>
+      </c>
+      <c r="B40" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="C40" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E40">
+        <v>809</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G40" t="str">
+        <v>felipe donoso</v>
+      </c>
+      <c r="H40">
+        <v>2781</v>
+      </c>
+      <c r="I40">
+        <v>2641.95</v>
+      </c>
+      <c r="J40">
+        <v>10</v>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>COT-2026-0001</v>
+      </c>
+      <c r="B41" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="C41" t="str">
+        <v>ALTO BUZETA (MT)</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Cerrillos</v>
+      </c>
+      <c r="E41">
+        <v>808</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Departamento</v>
+      </c>
+      <c r="G41" t="str">
+        <v>juan perez</v>
+      </c>
+      <c r="H41">
+        <v>2781</v>
+      </c>
+      <c r="I41">
+        <v>2502.9</v>
+      </c>
+      <c r="J41">
+        <v>10</v>
+      </c>
+      <c r="K41" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K41"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Historial_cotizaciones.xlsx
+++ b/Historial_cotizaciones.xlsx
@@ -479,7 +479,7 @@
         <v>10</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="3">
@@ -514,7 +514,7 @@
         <v>10</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>Gianfranco</v>
       </c>
     </row>
     <row r="4">
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>MTZ</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>mtz</v>
       </c>
     </row>
     <row r="6">
@@ -619,7 +619,7 @@
         <v>10</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>gf</v>
       </c>
     </row>
     <row r="7">
@@ -654,7 +654,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="8">
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="9">
@@ -724,7 +724,7 @@
         <v>10</v>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="10">
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="11">
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="12">
@@ -829,7 +829,7 @@
         <v>10</v>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="13">
@@ -864,7 +864,7 @@
         <v>10</v>
       </c>
       <c r="K13" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="14">
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="15">
@@ -934,7 +934,7 @@
         <v>10</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="16">
@@ -969,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="17">
@@ -1004,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="18">
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="19">
@@ -1074,7 +1074,7 @@
         <v>10</v>
       </c>
       <c r="K19" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="20">
@@ -1109,7 +1109,7 @@
         <v>10</v>
       </c>
       <c r="K20" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         <v>10</v>
       </c>
       <c r="K21" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="22">
@@ -1179,7 +1179,7 @@
         <v>10</v>
       </c>
       <c r="K22" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="23">
@@ -1214,7 +1214,7 @@
         <v>10</v>
       </c>
       <c r="K23" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="24">
@@ -1249,7 +1249,7 @@
         <v>10</v>
       </c>
       <c r="K24" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="25">
@@ -1284,7 +1284,7 @@
         <v>10</v>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="26">
@@ -1319,7 +1319,7 @@
         <v>10</v>
       </c>
       <c r="K26" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="27">
@@ -1354,7 +1354,7 @@
         <v>10</v>
       </c>
       <c r="K27" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="28">
@@ -1389,7 +1389,7 @@
         <v>10</v>
       </c>
       <c r="K28" t="str">
-        <v/>
+        <v>Felipe Donoso</v>
       </c>
     </row>
     <row r="29">
@@ -1424,7 +1424,7 @@
         <v>10</v>
       </c>
       <c r="K29" t="str">
-        <v/>
+        <v>FD</v>
       </c>
     </row>
     <row r="30">
@@ -1459,7 +1459,7 @@
         <v>10</v>
       </c>
       <c r="K30" t="str">
-        <v/>
+        <v>Felipe Donoso</v>
       </c>
     </row>
     <row r="31">
@@ -1494,7 +1494,7 @@
         <v>10</v>
       </c>
       <c r="K31" t="str">
-        <v/>
+        <v>Felipe Donoso</v>
       </c>
     </row>
     <row r="32">
@@ -1529,7 +1529,7 @@
         <v>10</v>
       </c>
       <c r="K32" t="str">
-        <v/>
+        <v>Felipe Donoso</v>
       </c>
     </row>
     <row r="33">
@@ -1564,7 +1564,7 @@
         <v>10</v>
       </c>
       <c r="K33" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="34">
@@ -1599,7 +1599,7 @@
         <v>10</v>
       </c>
       <c r="K34" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="35">
@@ -1634,7 +1634,7 @@
         <v>10</v>
       </c>
       <c r="K35" t="str">
-        <v/>
+        <v>Felipe Donoso</v>
       </c>
     </row>
     <row r="36">
@@ -1669,7 +1669,7 @@
         <v>10</v>
       </c>
       <c r="K36" t="str">
-        <v/>
+        <v>fd</v>
       </c>
     </row>
     <row r="37">
@@ -1704,7 +1704,7 @@
         <v>10</v>
       </c>
       <c r="K37" t="str">
-        <v/>
+        <v>Felipe Donoso</v>
       </c>
     </row>
     <row r="38">
@@ -1739,7 +1739,7 @@
         <v>10</v>
       </c>
       <c r="K38" t="str">
-        <v/>
+        <v>MARIA TERESA ZEGERS</v>
       </c>
     </row>
     <row r="39">
